--- a/Exam/gymtrackerpro/lib/controller/__tests__/it/workout-session-controller/listMemberWorkoutSessions-it-form.xlsx
+++ b/Exam/gymtrackerpro/lib/controller/__tests__/it/workout-session-controller/listMemberWorkoutSessions-it-form.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="74">
   <si>
     <t>Statement: listMemberWorkoutSessions(memberId: string, options?: WorkoutSessionListOptions): Promise&lt;ActionResult&lt;PageResult&lt;WorkoutSessionWithExercises&gt;&gt;&gt; — delegates to workoutSessionService.listMemberWorkoutSessions() and returns the paginated result wrapped in ActionResult.</t>
   </si>
@@ -82,13 +82,14 @@
     <t>1</t>
   </si>
   <si>
-    <t>Member seeded via userService.createMember(). Exercise seeded via exerciseService.createExercise(). Three sessions seeded via workoutSessionService.createWorkoutSession(): dates "2024-01-01", "2024-03-01", "2024-06-01".</t>
-  </si>
-  <si>
-    <t>listMemberWorkoutSessions(seededMember.id)</t>
-  </si>
-  <si>
-    <t>{ success: true, data: { total: 3, items: ordered by date ASC } }</t>
+    <t xml:space="preserve">Member seeded via userService.createMember(). Exercise seeded via exerciseService.createExercise(). Three sessions seeded via workoutSessionService.createWorkoutSession(): dates "2024-03-01", "2024-01-01", "2024-06-01".
+const inputMemberId: string = seededMember.id</t>
+  </si>
+  <si>
+    <t>listMemberWorkoutSessions(inputMemberId)</t>
+  </si>
+  <si>
+    <t>{ success: true, data: { total: 3, items: ordered date ASC [2024-01-01, 2024-03-01, 2024-06-01] } }</t>
   </si>
   <si>
     <t>No change</t>
@@ -100,7 +101,8 @@
     <t>2</t>
   </si>
   <si>
-    <t>Member seeded via userService.createMember(). No sessions seeded.</t>
+    <t xml:space="preserve">Member seeded via userService.createMember(). No sessions seeded.
+const inputMemberId: string = seededMember.id</t>
   </si>
   <si>
     <t>{ success: true, data: { items: [], total: 0 } }</t>
@@ -109,14 +111,102 @@
     <t>3</t>
   </si>
   <si>
+    <t xml:space="preserve">Two members seeded via userService.createMember(): member1 (m1@gym.test), member2 (m2@gym.test). Exercise seeded via exerciseService.createExercise(). One session seeded for member1, one session seeded for member2 via workoutSessionService.createWorkoutSession().
+const inputMemberId: string = member1.id</t>
+  </si>
+  <si>
+    <t>{ success: true, data: { total: 1, items: [member1's session only] } }</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
     <t xml:space="preserve">Member seeded via userService.createMember(). Exercise seeded via exerciseService.createExercise(). Two sessions seeded: "2024-01-01", "2024-06-01".
-const options: WorkoutSessionListOptions = { startDate: new Date("2024-03-01") }</t>
-  </si>
-  <si>
-    <t>listMemberWorkoutSessions(seededMember.id, options)</t>
+const inputMemberId: string = seededMember.id
+const inputOptions: WorkoutSessionListOptions = { startDate: new Date("2024-03-01") }</t>
+  </si>
+  <si>
+    <t>listMemberWorkoutSessions(inputMemberId, inputOptions)</t>
   </si>
   <si>
     <t>{ success: true, data: { total: 1, items: [2024-06-01] } }</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Member seeded via userService.createMember(). Exercise seeded via exerciseService.createExercise(). Two sessions seeded: "2024-01-01", "2024-06-01".
+const inputMemberId: string = seededMember.id
+const inputOptions: WorkoutSessionListOptions = { endDate: new Date("2024-03-01") }</t>
+  </si>
+  <si>
+    <t>{ success: true, data: { total: 1, items: [2024-01-01] } }</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Member seeded via userService.createMember(). Exercise seeded via exerciseService.createExercise(). Three sessions seeded: "2024-01-01", "2024-04-01", "2024-08-01".
+const inputMemberId: string = seededMember.id
+const inputOptions: WorkoutSessionListOptions = { startDate: new Date("2024-03-01"), endDate: new Date("2024-06-01") }</t>
+  </si>
+  <si>
+    <t>{ success: true, data: { total: 1, items: [2024-04-01] } }</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two members seeded via userService.createMember(): member1 (m1@gym.test), member2 (m2@gym.test). Exercise seeded via exerciseService.createExercise(). Sessions seeded: member1 → "2024-01-01", member1 → "2024-06-01", member2 → "2024-06-01".
+const inputMemberId: string = member1.id
+const inputOptions: WorkoutSessionListOptions = { startDate: new Date("2024-03-01") }</t>
+  </si>
+  <si>
+    <t>{ success: true, data: { total: 1, items: [member1's 2024-06-01 session only] } } (member1's 2024-01-01 excluded by startDate; member2's 2024-06-01 excluded by memberId)</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Member seeded via userService.createMember(). Exercise seeded via exerciseService.createExercise(). Five sessions seeded: "2024-01-01" through "2024-05-01".
+const inputMemberId: string = seededMember.id
+const inputOptions: WorkoutSessionListOptions = { page: 2, pageSize: 2 }</t>
+  </si>
+  <si>
+    <t>{ success: true, data: { total: 5, items: [length 2, 2024-03-01, 2024-02-01] (date DESC) } }</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Member seeded via userService.createMember(). Exercise seeded via exerciseService.createExercise(). Three sessions seeded: "2024-01-01", "2024-02-01", "2024-03-01".
+const inputMemberId: string = seededMember.id
+const inputOptions: WorkoutSessionListOptions = { page: 0, pageSize: 2 }</t>
+  </si>
+  <si>
+    <t>{ success: true, data: { total: 3, items: [length 2, 2024-03-01, 2024-02-01] } } (page 0 clamped to page 1)</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Member seeded via userService.createMember(). Exercise seeded via exerciseService.createExercise(). Three sessions seeded: "2024-01-01", "2024-02-01", "2024-03-01".
+const inputMemberId: string = seededMember.id
+const inputOptions: WorkoutSessionListOptions = { page: 1, pageSize: 100 }</t>
+  </si>
+  <si>
+    <t>{ success: true, data: { total: 3, items: [length 3, first item 2024-03-01] (date DESC) } }</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Member seeded via userService.createMember(). Exercise seeded via exerciseService.createExercise(). Three sessions seeded: "2024-01-01", "2024-02-01", "2024-03-01".
+const inputMemberId: string = seededMember.id
+const inputOptions: WorkoutSessionListOptions = { page: 2 }</t>
+  </si>
+  <si>
+    <t>{ success: true, data: { total: 3, items: [length 3, 2024-01-01, 2024-02-01, 2024-03-01] } } (pageSize absent → not paginated, date ASC)</t>
   </si>
   <si>
     <t>Testing</t>
@@ -801,13 +891,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="80" customWidth="1"/>
-    <col min="4" max="4" width="55" customWidth="1"/>
-    <col min="5" max="5" width="69" customWidth="1"/>
+    <col min="4" max="4" width="58" customWidth="1"/>
+    <col min="5" max="5" width="80" customWidth="1"/>
     <col min="6" max="6" width="27" customWidth="1"/>
     <col min="7" max="7" width="17" customWidth="1"/>
   </cols>
@@ -858,7 +948,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" ht="35" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -881,7 +971,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" ht="65" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" ht="80" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -892,15 +982,199 @@
         <v>31</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>33</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>25</v>
       </c>
       <c r="G4" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" ht="65" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" ht="65" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" ht="80" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" ht="95" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" ht="65" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" ht="65" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" ht="65" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" ht="65" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G12" s="6" t="s">
         <v>26</v>
       </c>
     </row>
@@ -929,17 +1203,17 @@
         <v>1</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
@@ -951,40 +1225,40 @@
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>41</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -992,40 +1266,40 @@
         <v>1</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="C6" s="1">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D6" s="1">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E6" s="1">
         <v>0</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="J6" s="1">
         <v>0</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
